--- a/data/trans_dic/IP18A02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP18A02-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico</t>
+          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,91; 55,45</t>
+          <t>33,88; 55,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,02; 24,68</t>
+          <t>8,06; 23,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 21,36</t>
+          <t>7,05; 20,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,02</t>
+          <t>0,0; 33,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,72; 38,96</t>
+          <t>17,56; 38,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,39; 23,9</t>
+          <t>7,44; 24,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,5; 31,71</t>
+          <t>14,51; 33,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,19</t>
+          <t>0,0; 21,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,26; 42,51</t>
+          <t>28,46; 42,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 21,14</t>
+          <t>9,12; 20,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,22; 23,82</t>
+          <t>12,5; 24,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 22,38</t>
+          <t>2,26; 21,61</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,93; 18,47</t>
+          <t>7,37; 17,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,41; 19,37</t>
+          <t>8,24; 19,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,88; 17,99</t>
+          <t>6,6; 17,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 35,03</t>
+          <t>2,98; 34,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,06; 21,59</t>
+          <t>9,54; 21,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 17,22</t>
+          <t>6,63; 17,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,18; 22,17</t>
+          <t>9,42; 20,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 27,44</t>
+          <t>4,11; 24,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,26; 18,37</t>
+          <t>10,02; 18,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,75; 16,46</t>
+          <t>8,56; 15,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,84; 17,98</t>
+          <t>9,7; 17,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 24,81</t>
+          <t>6,12; 23,46</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,78; 28,1</t>
+          <t>11,73; 28,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,74; 32,7</t>
+          <t>16,95; 34,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,25; 28,55</t>
+          <t>11,69; 27,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,16</t>
+          <t>0,0; 32,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,92; 31,46</t>
+          <t>14,89; 30,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,99; 25,97</t>
+          <t>11,68; 25,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 16,87</t>
+          <t>3,53; 16,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,1</t>
+          <t>2,02; 27,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,2; 27,37</t>
+          <t>15,5; 27,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,29; 26,83</t>
+          <t>15,09; 26,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 19,94</t>
+          <t>9,73; 20,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 19,26</t>
+          <t>2,22; 19,77</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,97; 32,07</t>
+          <t>16,09; 31,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,74; 22,88</t>
+          <t>8,9; 23,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,4; 25,46</t>
+          <t>10,03; 25,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,12; 59,96</t>
+          <t>9,75; 59,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,51; 29,56</t>
+          <t>13,28; 29,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 12,3</t>
+          <t>3,3; 12,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 17,17</t>
+          <t>5,11; 16,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,13</t>
+          <t>0,0; 24,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,45; 28,67</t>
+          <t>16,81; 28,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 15,67</t>
+          <t>7,18; 15,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 18,54</t>
+          <t>9,23; 18,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 34,43</t>
+          <t>7,09; 37,43</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,25; 36,46</t>
+          <t>11,45; 35,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 17,02</t>
+          <t>1,71; 16,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,47; 40,3</t>
+          <t>16,34; 39,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,89; 34,85</t>
+          <t>11,02; 35,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,59; 31,56</t>
+          <t>11,47; 32,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,23; 43,41</t>
+          <t>20,14; 43,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,74</t>
+          <t>0,0; 54,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,17; 30,94</t>
+          <t>13,81; 30,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,28; 20,96</t>
+          <t>8,18; 21,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,5; 36,72</t>
+          <t>21,35; 36,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,05</t>
+          <t>0,0; 41,37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,88; 30,35</t>
+          <t>12,14; 30,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,45; 36,96</t>
+          <t>17,66; 37,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,54; 23,1</t>
+          <t>7,61; 23,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,06</t>
+          <t>0,0; 26,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,23; 29,5</t>
+          <t>11,81; 29,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,48; 25,79</t>
+          <t>8,62; 25,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,69; 23,33</t>
+          <t>7,59; 23,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,71; 33,26</t>
+          <t>5,53; 35,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,44; 28,03</t>
+          <t>14,07; 26,55</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,76; 27,7</t>
+          <t>14,59; 27,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,61; 19,87</t>
+          <t>9,08; 19,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,56; 26,39</t>
+          <t>5,44; 25,57</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,84; 33,87</t>
+          <t>21,25; 33,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,33; 34,03</t>
+          <t>21,27; 33,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,63; 32,19</t>
+          <t>19,86; 32,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,6; 35,6</t>
+          <t>6,74; 36,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,16; 29,17</t>
+          <t>16,39; 28,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,46; 31,59</t>
+          <t>19,65; 31,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,05; 35,79</t>
+          <t>21,97; 35,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,02; 36,89</t>
+          <t>9,85; 37,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,51; 29,27</t>
+          <t>20,69; 29,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,91; 30,93</t>
+          <t>22,09; 30,63</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22,36; 31,7</t>
+          <t>22,12; 31,76</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,0; 31,74</t>
+          <t>10,89; 30,85</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,64; 29,18</t>
+          <t>17,68; 29,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,87; 33,03</t>
+          <t>21,02; 32,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,79; 27,28</t>
+          <t>16,19; 27,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29,61; 74,1</t>
+          <t>29,84; 72,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,5; 24,64</t>
+          <t>12,98; 23,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,52; 32,71</t>
+          <t>21,35; 32,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,11; 28,59</t>
+          <t>17,75; 28,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,34; 68,99</t>
+          <t>31,39; 68,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,58; 24,79</t>
+          <t>16,68; 24,52</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22,89; 31,03</t>
+          <t>22,73; 30,76</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19,01; 26,12</t>
+          <t>18,45; 26,04</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>35,95; 63,97</t>
+          <t>36,55; 64,1</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20,49; 26,14</t>
+          <t>20,6; 26,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,62; 23,67</t>
+          <t>18,39; 23,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16,35; 21,45</t>
+          <t>16,56; 21,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,06; 25,97</t>
+          <t>13,49; 26,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,59; 22,95</t>
+          <t>17,85; 22,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,73; 21,33</t>
+          <t>16,33; 21,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,21; 22,19</t>
+          <t>17,29; 22,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,95; 25,5</t>
+          <t>13,64; 25,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,89; 23,62</t>
+          <t>19,73; 23,6</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18,19; 21,91</t>
+          <t>18,33; 21,93</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,69; 21,03</t>
+          <t>17,53; 21,15</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,12; 23,58</t>
+          <t>15,27; 23,54</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>22200</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7054</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6736</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1383</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14046</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8102</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12334</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>36245</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15157</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19070</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>17020; 28090</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3962; 11590</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3736; 10884</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4064</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9133; 20021</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4086; 13444</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8054; 18318</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3015</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>29105; 43684</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9494; 21693</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13555; 26669</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>592; 5651</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12732</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9991</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>14974</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10658</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14119</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1951</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>26113</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>23390</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>24110</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3982</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6748; 16263</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7851; 18975</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5793; 15740</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>406; 4681</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>9223; 20714</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6510; 16761</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8708; 19378</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>671; 3983</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>18851; 34510</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>16565; 30754</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>17477; 31949</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1833; 7028</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>12524</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>16089</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12624</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>14987</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12679</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5571</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>27511</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>28768</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>18194</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2431</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7433; 17951</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11427; 23483</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7624; 18180</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4587</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9998; 20568</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8319; 18400</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2218; 10147</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>331; 4494</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>20232; 35898</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>20924; 37235</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>12460; 25795</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>673; 6006</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>15750</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10948</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12234</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4075</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14137</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5377</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7849</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>29887</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>16325</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>20083</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5085</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>10841; 21541</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6437; 17051</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7284; 18256</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1293; 7840</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>9000; 19718</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2612; 9880</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4042; 13333</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3578</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>22724; 38446</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>10887; 23652</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>14002; 27861</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1983; 10465</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2291</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11271</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7013</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8826</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>13635</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>13976</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>11117</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24907</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>3676; 11275</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>661; 6221</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6833; 16524</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3546; 11326</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4966; 14184</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9038; 19479</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2905</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>8877; 19831</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>6701; 17634</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>18508; 31634</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3857</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>10249</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13997</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7236</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>9701</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>9375</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>7582</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2686</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>19950</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>23372</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>14818</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3425</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>6203; 15599</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9505; 20002</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3927; 11950</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2387</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>6002; 15045</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>5093; 15096</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4330; 13161</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>943; 6107</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>14345; 27056</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>16475; 31494</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>9858; 21523</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1424; 6696</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>33087</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>36631</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>28180</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>27665</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>35795</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>32190</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5788</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>60753</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>72426</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>60370</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>9899</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>25850; 40925</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>28725; 45249</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>22156; 36327</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1502; 8073</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>20293; 35116</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>28121; 44769</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>24698; 39873</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2730; 10489</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>50782; 72577</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>61437; 85194</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>49537; 71144</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5445; 15432</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>27728</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>40068</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>33857</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>6203</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>24042</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>43387</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>37754</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>10135</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>51771</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>83455</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>71611</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>16338</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>21324; 35313</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>31823; 48517</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>25551; 42827</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>3574; 8721</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>17333; 32038</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>34335; 52483</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>29418; 46479</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>6260; 13719</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>42393; 62345</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>70974; 96031</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>59700; 84247</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>11666; 20460</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>139640</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>139810</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>122128</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>19229</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>126565</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>134200</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>131035</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>25042</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>266205</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>274010</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>253163</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>44271</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>123195; 157361</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>121942; 157901</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>106202; 137208</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>13530; 26299</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>111383; 143189</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>115941; 151303</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>115814; 147761</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>17947; 33365</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>241130; 288357</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>251680; 301133</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>229916; 277317</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>35401; 54582</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP18A02-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,88; 55,91</t>
+          <t>33,8; 55,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,06; 23,56</t>
+          <t>7,68; 23,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 20,55</t>
+          <t>7,19; 21,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,61</t>
+          <t>0,0; 39,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,56; 38,49</t>
+          <t>18,11; 36,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,44; 24,48</t>
+          <t>8,11; 24,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,51; 33,0</t>
+          <t>14,29; 32,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,44</t>
+          <t>0,0; 21,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,46; 42,72</t>
+          <t>28,21; 43,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,12; 20,84</t>
+          <t>9,29; 21,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,5; 24,59</t>
+          <t>12,5; 24,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 21,61</t>
+          <t>2,24; 19,4</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,37; 17,76</t>
+          <t>7,4; 18,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,24; 19,91</t>
+          <t>8,57; 20,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 17,94</t>
+          <t>6,98; 19,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 34,34</t>
+          <t>3,06; 34,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,54; 21,43</t>
+          <t>10,18; 21,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 17,08</t>
+          <t>6,1; 16,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,42; 20,97</t>
+          <t>9,98; 21,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,11; 24,39</t>
+          <t>4,42; 28,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,02; 18,33</t>
+          <t>10,21; 17,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,56; 15,9</t>
+          <t>8,29; 16,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,7; 17,74</t>
+          <t>9,71; 18,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,12; 23,46</t>
+          <t>6,19; 23,77</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,73; 28,34</t>
+          <t>12,81; 29,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,95; 34,83</t>
+          <t>16,31; 33,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,69; 27,87</t>
+          <t>12,84; 28,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,86</t>
+          <t>0,0; 24,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,89; 30,63</t>
+          <t>14,89; 30,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,68; 25,82</t>
+          <t>11,49; 26,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 16,16</t>
+          <t>4,2; 16,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 27,36</t>
+          <t>2,34; 29,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,5; 27,51</t>
+          <t>15,78; 27,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,09; 26,85</t>
+          <t>15,37; 26,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,73; 20,15</t>
+          <t>9,87; 19,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 19,77</t>
+          <t>2,24; 18,52</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,09; 31,96</t>
+          <t>15,44; 32,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,9; 23,57</t>
+          <t>9,6; 23,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 25,14</t>
+          <t>9,94; 25,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,75; 59,09</t>
+          <t>12,23; 58,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,28; 29,09</t>
+          <t>13,67; 29,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 12,47</t>
+          <t>3,28; 13,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 16,85</t>
+          <t>4,86; 17,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,35</t>
+          <t>0,0; 24,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,81; 28,44</t>
+          <t>16,51; 28,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 15,61</t>
+          <t>7,32; 15,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 18,36</t>
+          <t>9,43; 18,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,09; 37,43</t>
+          <t>7,94; 36,39</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,45; 35,11</t>
+          <t>11,45; 34,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 16,11</t>
+          <t>1,72; 16,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,34; 39,52</t>
+          <t>16,96; 39,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,42 +1297,42 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,02; 35,21</t>
+          <t>11,06; 36,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,47; 32,77</t>
+          <t>11,75; 33,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,14; 43,4</t>
+          <t>20,15; 41,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,22</t>
+          <t>0,0; 54,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,81; 30,85</t>
+          <t>14,46; 31,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 21,53</t>
+          <t>8,17; 21,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,35; 36,49</t>
+          <t>21,6; 38,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,37</t>
+          <t>0,0; 34,29</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,14; 30,52</t>
+          <t>11,7; 30,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,66; 37,16</t>
+          <t>17,03; 36,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,61; 23,17</t>
+          <t>7,62; 24,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,14</t>
+          <t>0,0; 27,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,81; 29,61</t>
+          <t>11,52; 29,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,62; 25,55</t>
+          <t>8,7; 25,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,59; 23,08</t>
+          <t>6,57; 21,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,53; 35,81</t>
+          <t>6,21; 33,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,07; 26,55</t>
+          <t>13,76; 26,68</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,59; 27,89</t>
+          <t>14,75; 28,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,08; 19,82</t>
+          <t>9,31; 20,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,44; 25,57</t>
+          <t>5,61; 24,19</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,25; 33,65</t>
+          <t>21,23; 34,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,27; 33,51</t>
+          <t>21,76; 33,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,86; 32,57</t>
+          <t>18,95; 32,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,74; 36,22</t>
+          <t>6,32; 35,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,39; 28,35</t>
+          <t>16,73; 29,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,65; 31,28</t>
+          <t>19,69; 31,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,97; 35,46</t>
+          <t>22,02; 35,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,85; 37,83</t>
+          <t>8,86; 37,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,69; 29,57</t>
+          <t>20,52; 29,66</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22,09; 30,63</t>
+          <t>21,48; 29,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22,12; 31,76</t>
+          <t>22,22; 32,04</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,89; 30,85</t>
+          <t>10,49; 31,42</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,68; 29,27</t>
+          <t>17,22; 29,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,02; 32,05</t>
+          <t>21,19; 32,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,19; 27,14</t>
+          <t>16,49; 26,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29,84; 72,81</t>
+          <t>30,82; 74,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,98; 23,99</t>
+          <t>12,84; 23,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,35; 32,63</t>
+          <t>21,12; 33,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,75; 28,04</t>
+          <t>17,91; 28,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>31,39; 68,79</t>
+          <t>32,95; 68,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,68; 24,52</t>
+          <t>16,46; 24,29</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22,73; 30,76</t>
+          <t>23,03; 31,24</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,45; 26,04</t>
+          <t>18,56; 25,76</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,55; 64,1</t>
+          <t>36,39; 65,59</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20,6; 26,31</t>
+          <t>20,62; 26,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,39; 23,81</t>
+          <t>18,41; 23,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16,56; 21,4</t>
+          <t>16,58; 21,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,49; 26,22</t>
+          <t>13,56; 26,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,85; 22,95</t>
+          <t>17,79; 22,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,33; 21,32</t>
+          <t>16,39; 21,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,29; 22,06</t>
+          <t>16,97; 21,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,64; 25,35</t>
+          <t>14,04; 24,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,73; 23,6</t>
+          <t>20,12; 23,92</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18,33; 21,93</t>
+          <t>18,23; 21,91</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,53; 21,15</t>
+          <t>17,62; 21,17</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,27; 23,54</t>
+          <t>14,7; 23,52</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17020; 28090</t>
+          <t>16979; 27856</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3962; 11590</t>
+          <t>3776; 11471</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3736; 10884</t>
+          <t>3808; 11221</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4064</t>
+          <t>0; 4740</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9133; 20021</t>
+          <t>9419; 19211</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4086; 13444</t>
+          <t>4455; 13709</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8054; 18318</t>
+          <t>7934; 18182</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3015</t>
+          <t>0; 2956</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29105; 43684</t>
+          <t>28850; 44092</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9494; 21693</t>
+          <t>9668; 21894</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13555; 26669</t>
+          <t>13562; 26269</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>592; 5651</t>
+          <t>587; 5074</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6748; 16263</t>
+          <t>6777; 16491</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7851; 18975</t>
+          <t>8165; 19494</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5793; 15740</t>
+          <t>6127; 16813</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>406; 4681</t>
+          <t>418; 4654</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9223; 20714</t>
+          <t>9846; 21089</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6510; 16761</t>
+          <t>5987; 15897</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8708; 19378</t>
+          <t>9217; 20193</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>671; 3983</t>
+          <t>722; 4589</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18851; 34510</t>
+          <t>19225; 33590</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16565; 30754</t>
+          <t>16027; 31088</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17477; 31949</t>
+          <t>17484; 32998</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1833; 7028</t>
+          <t>1853; 7123</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7433; 17951</t>
+          <t>8113; 18743</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11427; 23483</t>
+          <t>10993; 22864</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7624; 18180</t>
+          <t>8376; 18822</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4587</t>
+          <t>0; 3393</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9998; 20568</t>
+          <t>9998; 20593</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8319; 18400</t>
+          <t>8185; 19021</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2218; 10147</t>
+          <t>2636; 10098</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>331; 4494</t>
+          <t>385; 4801</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20232; 35898</t>
+          <t>20596; 35298</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20924; 37235</t>
+          <t>21311; 36820</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12460; 25795</t>
+          <t>12637; 25370</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>673; 6006</t>
+          <t>680; 5625</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10841; 21541</t>
+          <t>10406; 21655</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6437; 17051</t>
+          <t>6945; 16646</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7284; 18256</t>
+          <t>7221; 18380</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1293; 7840</t>
+          <t>1622; 7790</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9000; 19718</t>
+          <t>9264; 20053</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2612; 9880</t>
+          <t>2602; 10297</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4042; 13333</t>
+          <t>3846; 13555</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3578</t>
+          <t>0; 3575</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22724; 38446</t>
+          <t>22312; 38282</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10887; 23652</t>
+          <t>11098; 23574</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14002; 27861</t>
+          <t>14312; 28250</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1983; 10465</t>
+          <t>2222; 10175</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3676; 11275</t>
+          <t>3675; 10997</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>661; 6221</t>
+          <t>665; 6236</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6833; 16524</t>
+          <t>7092; 16423</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,42 +3061,42 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3546; 11326</t>
+          <t>3558; 11819</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4966; 14184</t>
+          <t>5085; 14425</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9038; 19479</t>
+          <t>9044; 18707</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2905</t>
+          <t>0; 2929</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8877; 19831</t>
+          <t>9294; 20157</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6701; 17634</t>
+          <t>6691; 17196</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18508; 31634</t>
+          <t>18729; 33050</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3857</t>
+          <t>0; 3197</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6203; 15599</t>
+          <t>5978; 15585</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9505; 20002</t>
+          <t>9165; 19777</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3927; 11950</t>
+          <t>3931; 12422</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2387</t>
+          <t>0; 2483</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6002; 15045</t>
+          <t>5851; 14756</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5093; 15096</t>
+          <t>5139; 14782</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4330; 13161</t>
+          <t>3748; 12333</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>943; 6107</t>
+          <t>1059; 5642</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14345; 27056</t>
+          <t>14027; 27194</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16475; 31494</t>
+          <t>16651; 31610</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9858; 21523</t>
+          <t>10113; 21768</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1424; 6696</t>
+          <t>1470; 6334</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25850; 40925</t>
+          <t>25821; 41649</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28725; 45249</t>
+          <t>29375; 45574</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22156; 36327</t>
+          <t>21139; 35699</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1502; 8073</t>
+          <t>1409; 7942</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20293; 35116</t>
+          <t>20721; 36733</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28121; 44769</t>
+          <t>28175; 45270</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24698; 39873</t>
+          <t>24762; 40097</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2730; 10489</t>
+          <t>2457; 10407</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>50782; 72577</t>
+          <t>50362; 72801</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61437; 85194</t>
+          <t>59732; 82266</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49537; 71144</t>
+          <t>49758; 71757</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5445; 15432</t>
+          <t>5245; 15716</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>21324; 35313</t>
+          <t>20775; 35193</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>31823; 48517</t>
+          <t>32076; 49461</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25551; 42827</t>
+          <t>26020; 42145</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3574; 8721</t>
+          <t>3692; 8978</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>17333; 32038</t>
+          <t>17147; 31262</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>34335; 52483</t>
+          <t>33971; 53577</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29418; 46479</t>
+          <t>29687; 47219</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6260; 13719</t>
+          <t>6571; 13626</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>42393; 62345</t>
+          <t>41843; 61751</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70974; 96031</t>
+          <t>71911; 97530</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>59700; 84247</t>
+          <t>60054; 83354</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>11666; 20460</t>
+          <t>11617; 20935</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>123195; 157361</t>
+          <t>123311; 156291</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>121942; 157901</t>
+          <t>122091; 157209</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>106202; 137208</t>
+          <t>106331; 139069</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13530; 26299</t>
+          <t>13605; 26560</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>111383; 143189</t>
+          <t>110984; 143305</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>115941; 151303</t>
+          <t>116359; 152330</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>115814; 147761</t>
+          <t>113675; 147131</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>17947; 33365</t>
+          <t>18472; 32847</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>241130; 288357</t>
+          <t>245853; 292357</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>251680; 301133</t>
+          <t>250288; 300829</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>229916; 277317</t>
+          <t>231019; 277629</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>35401; 54582</t>
+          <t>34095; 54546</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A02-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP18A02-Provincia-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22,22%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>44,19%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>14,34%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>12,72%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,44%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>27,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,22%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,8; 55,44</t>
+          <t>17,72; 38,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 23,32</t>
+          <t>8,39; 23,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 21,19</t>
+          <t>13,5; 31,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,21</t>
+          <t>0,0; 24,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,11; 36,93</t>
+          <t>33,91; 55,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,11; 24,96</t>
+          <t>8,02; 24,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,29; 32,75</t>
+          <t>6,83; 21,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,02</t>
+          <t>0,0; 39,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,21; 43,12</t>
+          <t>28,26; 42,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,29; 21,03</t>
+          <t>9,24; 21,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,5; 24,22</t>
+          <t>12,22; 23,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 19,4</t>
+          <t>2,5; 23,82</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,86%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15,28%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>12,17%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>13,36%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>11,39%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,9%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>15,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,86%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,28%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 18,01</t>
+          <t>10,06; 21,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,57; 20,46</t>
+          <t>6,06; 17,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,98; 19,17</t>
+          <t>10,18; 22,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 34,15</t>
+          <t>3,66; 24,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,18; 21,81</t>
+          <t>7,93; 18,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 16,2</t>
+          <t>8,41; 19,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,98; 21,85</t>
+          <t>6,88; 17,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 28,1</t>
+          <t>4,75; 35,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,21; 17,85</t>
+          <t>10,26; 18,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,29; 16,07</t>
+          <t>8,75; 16,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,71; 18,32</t>
+          <t>9,84; 17,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 23,77</t>
+          <t>6,03; 24,69</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22,32%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17,79%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9,99%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>19,77%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>23,87%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>19,35%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,32%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,87%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,81; 29,59</t>
+          <t>14,92; 31,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,31; 33,92</t>
+          <t>10,99; 25,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,84; 28,85</t>
+          <t>4,24; 16,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,31</t>
+          <t>2,07; 26,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,89; 30,67</t>
+          <t>12,78; 28,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,49; 26,69</t>
+          <t>15,74; 32,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 16,08</t>
+          <t>12,25; 28,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 29,24</t>
+          <t>0,0; 24,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,78; 27,05</t>
+          <t>16,2; 27,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,37; 26,55</t>
+          <t>15,29; 26,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,87; 19,82</t>
+          <t>9,23; 19,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 18,52</t>
+          <t>2,05; 18,16</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20,86%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>23,37%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>15,13%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>16,85%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30,71%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,86%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,44; 32,13</t>
+          <t>13,51; 29,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,6; 23,01</t>
+          <t>3,27; 12,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,94; 25,31</t>
+          <t>4,78; 17,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,23; 58,71</t>
+          <t>0,0; 23,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,67; 29,59</t>
+          <t>15,97; 32,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 13,0</t>
+          <t>8,74; 22,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 17,13</t>
+          <t>10,4; 25,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,33</t>
+          <t>10,79; 61,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,51; 28,32</t>
+          <t>16,45; 28,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 15,55</t>
+          <t>7,12; 15,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,43; 18,62</t>
+          <t>9,24; 18,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 36,39</t>
+          <t>6,95; 36,24</t>
         </is>
       </c>
     </row>
@@ -1209,44 +1209,44 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>21,8%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20,39%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30,38%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>20,61%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>21,69%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,93%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>26,96%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>21,8%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>20,39%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>30,38%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>20,17%</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t>21,74%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,45; 34,25</t>
+          <t>10,89; 34,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 16,15</t>
+          <t>10,59; 31,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,96; 39,28</t>
+          <t>20,23; 43,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 55,65</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,25; 36,46</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,73; 17,02</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,47; 40,3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11,06; 36,75</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,75; 33,33</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,15; 41,68</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 54,68</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,46; 31,36</t>
+          <t>14,17; 30,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,17; 21,0</t>
+          <t>8,28; 20,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,6; 38,12</t>
+          <t>21,5; 36,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,29</t>
+          <t>0,0; 31,36</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19,09%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15,87%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>16,61%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>20,05%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>26,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>14,03%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19,09%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,7; 30,49</t>
+          <t>11,23; 29,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,03; 36,74</t>
+          <t>8,48; 25,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,62; 24,08</t>
+          <t>6,69; 23,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,18</t>
+          <t>5,92; 36,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,52; 29,04</t>
+          <t>11,88; 30,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,7; 25,02</t>
+          <t>17,45; 36,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,57; 21,63</t>
+          <t>7,54; 23,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,21; 33,08</t>
+          <t>0,0; 25,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,76; 26,68</t>
+          <t>14,44; 28,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,75; 28,0</t>
+          <t>14,76; 27,7</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,31; 20,04</t>
+          <t>8,61; 19,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,61; 24,19</t>
+          <t>5,36; 26,58</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22,34%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25,01%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28,63%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20,9%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>27,2%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>27,13%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>25,26%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18,44%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>22,34%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,01%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>28,63%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,23; 34,25</t>
+          <t>17,16; 29,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,76; 33,75</t>
+          <t>19,46; 31,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,95; 32,0</t>
+          <t>22,05; 35,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,32; 35,63</t>
+          <t>8,69; 37,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,73; 29,66</t>
+          <t>20,84; 33,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,69; 31,63</t>
+          <t>21,33; 34,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,02; 35,66</t>
+          <t>18,63; 32,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,86; 37,54</t>
+          <t>8,02; 38,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,52; 29,66</t>
+          <t>20,51; 29,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,48; 29,58</t>
+          <t>21,91; 30,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22,22; 32,04</t>
+          <t>22,36; 31,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,49; 31,42</t>
+          <t>11,83; 33,95</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>18,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>26,98%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>22,78%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>50,94%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>22,98%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>26,47%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>21,45%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>51,79%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>18,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,22; 29,17</t>
+          <t>13,5; 24,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,19; 32,67</t>
+          <t>21,52; 32,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,49; 26,71</t>
+          <t>18,11; 28,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30,82; 74,96</t>
+          <t>31,35; 70,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,84; 23,4</t>
+          <t>17,64; 29,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,12; 33,31</t>
+          <t>20,87; 33,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,91; 28,49</t>
+          <t>16,79; 27,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,95; 68,33</t>
+          <t>32,84; 77,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,46; 24,29</t>
+          <t>16,58; 24,79</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,03; 31,24</t>
+          <t>22,89; 31,03</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,56; 25,76</t>
+          <t>19,01; 26,12</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,39; 65,59</t>
+          <t>36,26; 65,41</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>18,91%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>23,35%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>21,09%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>19,04%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>19,17%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>20,28%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>18,91%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>19,56%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20,62; 26,13</t>
+          <t>17,59; 22,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,41; 23,71</t>
+          <t>16,73; 21,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16,58; 21,69</t>
+          <t>17,21; 22,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,56; 26,48</t>
+          <t>14,2; 26,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,79; 22,97</t>
+          <t>20,49; 26,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,39; 21,46</t>
+          <t>18,62; 23,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,97; 21,96</t>
+          <t>16,35; 21,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,04; 24,96</t>
+          <t>13,93; 27,68</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,12; 23,92</t>
+          <t>19,89; 23,62</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18,23; 21,91</t>
+          <t>18,19; 21,91</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,62; 21,17</t>
+          <t>17,69; 21,03</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,7; 23,52</t>
+          <t>15,77; 24,6</t>
         </is>
       </c>
     </row>
@@ -1951,13 +1951,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14046</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8102</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12334</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>22200</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>7054</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>6736</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1383</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>14046</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8102</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12334</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>1964</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16979; 27856</t>
+          <t>9219; 20268</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3776; 11471</t>
+          <t>4608; 13126</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3808; 11221</t>
+          <t>7492; 17603</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4740</t>
+          <t>0; 2989</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9419; 19211</t>
+          <t>17035; 27860</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4455; 13709</t>
+          <t>3944; 12139</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7934; 18182</t>
+          <t>3617; 11311</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2956</t>
+          <t>0; 4349</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28850; 44092</t>
+          <t>28897; 43474</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9668; 21894</t>
+          <t>9617; 22010</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13562; 26269</t>
+          <t>13252; 25835</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>587; 5074</t>
+          <t>582; 5548</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14974</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10658</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14119</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1471</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11139</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12732</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9991</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14974</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10658</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14119</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3362</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6777; 16491</t>
+          <t>9727; 20873</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8165; 19494</t>
+          <t>5949; 16897</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6127; 16813</t>
+          <t>9407; 20482</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>418; 4654</t>
+          <t>527; 3529</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9846; 21089</t>
+          <t>7264; 16909</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5987; 15897</t>
+          <t>8018; 18454</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9217; 20193</t>
+          <t>6035; 15786</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>722; 4589</t>
+          <t>623; 4617</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19225; 33590</t>
+          <t>19303; 34571</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16027; 31088</t>
+          <t>16926; 31834</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17484; 32998</t>
+          <t>17726; 32391</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1853; 7123</t>
+          <t>1661; 6797</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>14987</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12679</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5571</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>12524</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>16089</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>12624</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>14987</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12679</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5571</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>675</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t>2077</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8113; 18743</t>
+          <t>10018; 21128</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10993; 22864</t>
+          <t>7830; 18506</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8376; 18822</t>
+          <t>2663; 10593</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3393</t>
+          <t>291; 3677</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9998; 20593</t>
+          <t>8099; 17800</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8185; 19021</t>
+          <t>10609; 22043</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2636; 10098</t>
+          <t>7994; 18627</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>385; 4801</t>
+          <t>0; 3280</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20596; 35298</t>
+          <t>21145; 35721</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21311; 36820</t>
+          <t>21208; 37204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12637; 25370</t>
+          <t>11819; 25534</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>680; 5625</t>
+          <t>567; 5016</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14137</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5377</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7849</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>15750</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>10948</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>12234</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4075</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14137</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5377</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7849</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5318</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10406; 21655</t>
+          <t>9155; 20033</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6945; 16646</t>
+          <t>2592; 9743</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7221; 18380</t>
+          <t>3781; 13587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1622; 7790</t>
+          <t>0; 3296</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9264; 20053</t>
+          <t>10761; 21617</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2602; 10297</t>
+          <t>6326; 16547</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3846; 13555</t>
+          <t>7550; 18488</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3575</t>
+          <t>1427; 8093</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22312; 38282</t>
+          <t>22229; 38747</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11098; 23574</t>
+          <t>10789; 23750</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14312; 28250</t>
+          <t>14015; 28137</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2222; 10175</t>
+          <t>1887; 9846</t>
         </is>
       </c>
     </row>
@@ -2910,37 +2910,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,44 +2973,44 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>7013</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8826</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13635</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>6963</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2291</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>11271</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>7013</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8826</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>13635</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
           <t>13976</t>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1106</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3675; 10997</t>
+          <t>3504; 11211</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>665; 6236</t>
+          <t>4583; 13660</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7092; 16423</t>
+          <t>9081; 19484</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>0; 2987</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3613; 11705</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>669; 6572</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6884; 16849</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3558; 11819</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5085; 14425</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9044; 18707</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0; 2929</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9294; 20157</t>
+          <t>9106; 19889</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6691; 17196</t>
+          <t>6781; 17164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18729; 33050</t>
+          <t>18639; 31834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3197</t>
+          <t>0; 3011</t>
         </is>
       </c>
     </row>
@@ -3118,37 +3118,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>9701</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9375</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7582</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2407</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>10249</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>13997</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>7236</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>9701</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9375</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>7582</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>582</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>2989</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5978; 15585</t>
+          <t>5707; 14987</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9165; 19777</t>
+          <t>5008; 15238</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3931; 12422</t>
+          <t>3815; 13304</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2483</t>
+          <t>858; 5286</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5851; 14756</t>
+          <t>6070; 15511</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5139; 14782</t>
+          <t>9395; 19894</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3748; 12333</t>
+          <t>3889; 11914</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1059; 5642</t>
+          <t>0; 2312</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14027; 27194</t>
+          <t>14717; 28567</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16651; 31610</t>
+          <t>16661; 31279</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10113; 21768</t>
+          <t>9352; 21585</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1470; 6334</t>
+          <t>1260; 6247</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>27665</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>35795</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>32190</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5821</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>33087</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>36631</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>28180</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>27665</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>35795</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>32190</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>10003</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25821; 41649</t>
+          <t>21247; 36124</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>29375; 45574</t>
+          <t>27843; 45202</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21139; 35699</t>
+          <t>24795; 40242</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1409; 7942</t>
+          <t>2421; 10323</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20721; 36733</t>
+          <t>25349; 41199</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28175; 45270</t>
+          <t>28795; 45950</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24762; 40097</t>
+          <t>20786; 35901</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2457; 10407</t>
+          <t>1592; 7650</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>50362; 72801</t>
+          <t>50351; 71842</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>59732; 82266</t>
+          <t>60933; 86018</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49758; 71757</t>
+          <t>50085; 71004</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5245; 15716</t>
+          <t>5640; 16192</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>24042</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>43387</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>37754</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>9902</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>27728</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>40068</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>33857</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>6203</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>43387</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>37754</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>16245</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20775; 35193</t>
+          <t>18029; 32914</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>32076; 49461</t>
+          <t>34604; 52606</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26020; 42145</t>
+          <t>30015; 47376</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3692; 8978</t>
+          <t>6095; 13644</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>17147; 31262</t>
+          <t>21286; 35198</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33971; 53577</t>
+          <t>31589; 49998</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29687; 47219</t>
+          <t>26498; 43051</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6571; 13626</t>
+          <t>3740; 8807</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>41843; 61751</t>
+          <t>42144; 63025</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>71911; 97530</t>
+          <t>71466; 96874</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>60054; 83354</t>
+          <t>61493; 84494</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>11617; 20935</t>
+          <t>11180; 20165</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>189</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>126565</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>134200</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>131035</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>23565</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>139640</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>139810</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>122128</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>19229</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>126565</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>134200</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>131035</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>44271</t>
+          <t>43065</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>123311; 156291</t>
+          <t>109774; 143230</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>122091; 157209</t>
+          <t>118759; 151405</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>106331; 139069</t>
+          <t>115286; 148676</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13605; 26560</t>
+          <t>17290; 32281</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>110984; 143305</t>
+          <t>122547; 156306</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>116359; 152330</t>
+          <t>123450; 156938</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>113675; 147131</t>
+          <t>104847; 137562</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>18472; 32847</t>
+          <t>13305; 26436</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>245853; 292357</t>
+          <t>243041; 288656</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>250288; 300829</t>
+          <t>249664; 300786</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>231019; 277629</t>
+          <t>231902; 275777</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>34095; 54546</t>
+          <t>34266; 53446</t>
         </is>
       </c>
     </row>
